--- a/reports/devops-juniors-israel-2026-W38.xlsx
+++ b/reports/devops-juniors-israel-2026-W38.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-14T12:35:07</t>
+    <t xml:space="preserve">2026-09-15T11:38:01</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -199,7 +199,421 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
-    <t xml:space="preserve">Devops Student</t>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator 7992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceva, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia/Scotland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PassportCard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-passportcard-4458103759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Operations &amp; Monitoring Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-monitoring-specialist-at-confidential-careers-4465521603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
   </si>
   <si>
     <t xml:space="preserve">Nice</t>
@@ -208,444 +622,6 @@
     <t xml:space="preserve">Israel - Raanana</t>
   </si>
   <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 243425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Azure, Cloud (any), Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-243425-at-experis-israel-4461821675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator 7992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communication System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceva, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">peax dorcom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-peax-dorcom-4464776806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tata Consultancy Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PassportCard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-passportcard-4458103759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4463461048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud (any)</t>
   </si>
   <si>
@@ -727,15 +703,15 @@
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
@@ -754,16 +730,22 @@
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
     <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
     <t xml:space="preserve">Docker</t>
@@ -772,22 +754,16 @@
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Windows Server</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -948,7 +924,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -972,7 +948,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>494</v>
+        <v>488</v>
       </c>
     </row>
     <row r="10">
@@ -1054,7 +1030,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -1062,7 +1038,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
@@ -1112,7 +1088,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30">
@@ -1120,7 +1096,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -1289,25 +1265,25 @@
         <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="3">
+        <v>80</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="3">
-        <v>83</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -1315,19 +1291,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>69</v>
@@ -1339,7 +1315,7 @@
         <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -1347,31 +1323,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="3">
+        <v>68</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="3">
-        <v>70</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -1385,25 +1361,25 @@
         <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="3">
+        <v>61</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="3">
-        <v>68</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>81</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="9">
@@ -1411,19 +1387,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="3">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>85</v>
@@ -1484,10 +1460,10 @@
         <v>96</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F11" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>97</v>
@@ -1516,10 +1492,10 @@
         <v>102</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>103</v>
@@ -1548,10 +1524,10 @@
         <v>108</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>109</v>
@@ -1563,7 +1539,7 @@
         <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>111</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -1571,31 +1547,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="D14" s="3" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1603,31 +1579,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3">
+        <v>32</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="3">
-        <v>39</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1635,10 +1611,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>53</v>
@@ -1647,19 +1623,19 @@
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1667,31 +1643,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>129</v>
+        <v>47</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
     </row>
     <row r="18">
@@ -1699,31 +1675,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3">
+        <v>27</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="3">
-        <v>28</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -1731,31 +1707,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F19" s="3">
+        <v>27</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F19" s="3">
-        <v>28</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="20">
@@ -1769,25 +1745,25 @@
         <v>141</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21">
@@ -1795,31 +1771,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="22">
@@ -1827,13 +1803,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>152</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>153</v>
+        <v>96</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -1842,16 +1818,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="23">
@@ -1859,31 +1835,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F23" s="3">
+        <v>23</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="3">
-        <v>24</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="24">
@@ -1891,31 +1867,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G24" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25">
@@ -1923,31 +1899,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26">
@@ -1955,31 +1931,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>53</v>
+        <v>170</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F26" s="3">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2032,7 +2008,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2047,22 +2023,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="2">
@@ -2085,7 +2061,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2097,7 +2073,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -2120,7 +2096,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2132,7 +2108,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -2155,7 +2131,7 @@
         <v>59</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2167,7 +2143,7 @@
         <v>50</v>
       </c>
       <c r="K4" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -2178,54 +2154,54 @@
         <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3">
+        <v>80</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="3">
-        <v>83</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="K5" s="3">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E6" s="3">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2234,45 +2210,45 @@
         <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="K6" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="3">
+        <v>68</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="3">
-        <v>70</v>
-      </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="K7" s="3">
-        <v>25</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -2283,54 +2259,54 @@
         <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="3">
+        <v>61</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="3">
-        <v>68</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="K8" s="3">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="3">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2342,7 +2318,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10">
@@ -2365,7 +2341,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2377,7 +2353,7 @@
         <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -2391,16 +2367,16 @@
         <v>96</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E11" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2412,7 +2388,7 @@
         <v>99</v>
       </c>
       <c r="K11" s="3">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -2426,16 +2402,16 @@
         <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2447,7 +2423,7 @@
         <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -2461,16 +2437,16 @@
         <v>108</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2479,88 +2455,88 @@
         <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>111</v>
+        <v>50</v>
       </c>
       <c r="K13" s="3">
-        <v>13</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="C14" s="3" t="s">
-        <v>114</v>
+        <v>53</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="K14" s="3">
-        <v>8</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3">
+        <v>32</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="3">
-        <v>39</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="K15" s="3">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>53</v>
@@ -2569,130 +2545,130 @@
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="J16" s="3" t="s">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="K16" s="3">
-        <v>63</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>129</v>
+        <v>47</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="K17" s="3">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="3">
+        <v>27</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3">
-        <v>28</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="K18" s="3">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="D19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="3">
+        <v>27</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="3">
-        <v>28</v>
-      </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="K19" s="3">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20">
@@ -2703,77 +2679,77 @@
         <v>141</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>108</v>
+        <v>142</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K20" s="3">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K21" s="3">
-        <v>18</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>151</v>
+        <v>111</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>152</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>153</v>
+        <v>96</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
@@ -2782,547 +2758,477 @@
         <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="K22" s="3">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E23" s="3">
+        <v>23</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="3">
-        <v>24</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="K23" s="3">
-        <v>29</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>165</v>
+        <v>105</v>
       </c>
       <c r="K24" s="3">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K25" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>53</v>
+        <v>170</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E26" s="3">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="K26" s="3">
-        <v>3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>122</v>
+        <v>179</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="3">
+        <v>9</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="3">
-        <v>12</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="J27" s="3" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="K27" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E28" s="3">
+        <v>8</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="3">
-        <v>12</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="K28" s="3">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" s="3">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="J29" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E29" s="3">
-        <v>10</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>193</v>
-      </c>
       <c r="K29" s="3">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3">
+        <v>8</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="J30" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="3">
-        <v>9</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="K30" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>46</v>
+        <v>197</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
         <v>8</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="K31" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="D32" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="3">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="C32" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="3">
-        <v>8</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="K32" s="3">
-        <v>4</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>114</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="K33" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>62</v>
+        <v>211</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>63</v>
+        <v>212</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E34" s="3">
-        <v>4</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>210</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K34" s="3">
-        <v>74</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E35" s="3">
-        <v>4</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>216</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>34</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="K35" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="3">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="K36" s="3">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E37" s="3">
-        <v>0</v>
-      </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="K37" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K37"/>
+  <autoFilter ref="A1:K35"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3358,8 +3264,6 @@
     <hyperlink ref="I33" r:id="rId32"/>
     <hyperlink ref="I34" r:id="rId33"/>
     <hyperlink ref="I35" r:id="rId34"/>
-    <hyperlink ref="I36" r:id="rId35"/>
-    <hyperlink ref="I37" r:id="rId36"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3367,11 +3271,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
+    <col min="5" max="5" width="29" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3390,10 +3294,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3401,48 +3305,48 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>131</v>
+        <v>194</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>166</v>
+        <v>196</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>170</v>
+        <v>198</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>132</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>
@@ -3457,185 +3361,185 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="B3" s="3">
         <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="B4" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>187</v>
+        <v>166</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>237</v>
+        <v>208</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B10" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -3655,10 +3559,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
     <row r="2">
@@ -3666,10 +3570,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3">
@@ -3677,10 +3581,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
     </row>
     <row r="4">
@@ -3691,7 +3595,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5">
@@ -3702,7 +3606,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
     </row>
     <row r="6">
@@ -3713,7 +3617,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7">
@@ -3724,7 +3628,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -3745,13 +3649,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2">
@@ -3759,10 +3663,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3771,10 +3675,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3786,7 +3690,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W38.xlsx
+++ b/reports/devops-juniors-israel-2026-W38.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="267">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-15T11:38:01</t>
+    <t xml:space="preserve">2026-09-16T11:24:46</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -187,6 +187,24 @@
     <t xml:space="preserve">2026-09-09</t>
   </si>
   <si>
+    <t xml:space="preserve">Associate Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/associate-development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Team Leader</t>
   </si>
   <si>
@@ -262,6 +280,21 @@
     <t xml:space="preserve">2026-08-31</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Analyst | Splunk &amp; Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-splunk-infrastructure-at-confidential-careers-4465957826</t>
+  </si>
+  <si>
     <t xml:space="preserve">Technical Support Specialist</t>
   </si>
   <si>
@@ -454,34 +487,28 @@
     <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
     <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
   </si>
   <si>
     <t xml:space="preserve">Oracle</t>
   </si>
   <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4444274357</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
@@ -508,6 +535,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Israel</t>
   </si>
   <si>
@@ -535,24 +580,6 @@
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior System Administrator</t>
   </si>
   <si>
@@ -589,30 +616,18 @@
     <t xml:space="preserve">2026-09-10</t>
   </si>
   <si>
-    <t xml:space="preserve">IT Operations &amp; Monitoring Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-monitoring-specialist-at-confidential-careers-4465521603</t>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-15</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
-  </si>
-  <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
   </si>
   <si>
@@ -703,15 +718,15 @@
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
@@ -754,16 +769,16 @@
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
-    <t xml:space="preserve">Windows Server</t>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
   </si>
   <si>
     <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -924,7 +939,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -948,7 +963,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>488</v>
+        <v>479</v>
       </c>
     </row>
     <row r="10">
@@ -1030,7 +1045,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -1088,7 +1103,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30">
@@ -1233,7 +1248,7 @@
         <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>25</v>
@@ -1242,16 +1257,16 @@
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -1259,10 +1274,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>53</v>
@@ -1271,19 +1286,19 @@
         <v>25</v>
       </c>
       <c r="F5" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
@@ -1291,19 +1306,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>69</v>
@@ -1315,7 +1330,7 @@
         <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7">
@@ -1323,31 +1338,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -1361,25 +1376,25 @@
         <v>78</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9">
@@ -1387,19 +1402,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="3">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>85</v>
@@ -1428,10 +1443,10 @@
         <v>90</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>91</v>
@@ -1443,7 +1458,7 @@
         <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11">
@@ -1451,31 +1466,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="3">
+        <v>47</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11" s="3">
-        <v>46</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -1483,31 +1498,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="3">
+        <v>47</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" s="3">
-        <v>44</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -1515,31 +1530,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="3">
+        <v>46</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="3">
-        <v>39</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -1553,25 +1568,25 @@
         <v>112</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
@@ -1579,31 +1594,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1611,10 +1626,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>53</v>
@@ -1623,19 +1638,19 @@
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>50</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17">
@@ -1643,31 +1658,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>47</v>
+        <v>129</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -1675,31 +1690,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19">
@@ -1707,31 +1722,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>136</v>
+        <v>47</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20">
@@ -1745,25 +1760,25 @@
         <v>141</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3">
+        <v>27</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="3">
-        <v>24</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>144</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="21">
@@ -1771,31 +1786,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F21" s="3">
+        <v>27</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="3">
-        <v>24</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="22">
@@ -1803,13 +1818,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>152</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -1818,16 +1833,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23">
@@ -1835,19 +1850,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>157</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>158</v>
@@ -1867,31 +1882,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25">
@@ -1899,31 +1914,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26">
@@ -1931,31 +1946,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>172</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -2073,7 +2088,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -2108,7 +2123,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2119,7 +2134,7 @@
         <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>25</v>
@@ -2128,7 +2143,7 @@
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>178</v>
@@ -2137,21 +2152,21 @@
         <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>53</v>
@@ -2160,10 +2175,10 @@
         <v>25</v>
       </c>
       <c r="E5" s="3">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>178</v>
@@ -2172,30 +2187,30 @@
         <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="K5" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>69</v>
@@ -2210,45 +2225,45 @@
         <v>70</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>178</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="K7" s="3">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -2259,48 +2274,48 @@
         <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>178</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="3">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>85</v>
@@ -2332,10 +2347,10 @@
         <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>91</v>
@@ -2350,30 +2365,30 @@
         <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="K10" s="3">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="3">
+        <v>47</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E11" s="3">
-        <v>46</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>178</v>
@@ -2382,33 +2397,33 @@
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="K11" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="3">
+        <v>47</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="3">
-        <v>44</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>178</v>
@@ -2417,33 +2432,33 @@
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="K12" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="3">
+        <v>46</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="3">
-        <v>39</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>178</v>
@@ -2452,13 +2467,13 @@
         <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="K13" s="3">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -2469,16 +2484,16 @@
         <v>112</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>178</v>
@@ -2487,33 +2502,33 @@
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K14" s="3">
-        <v>64</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>178</v>
@@ -2522,21 +2537,21 @@
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="K15" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>53</v>
@@ -2545,10 +2560,10 @@
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>178</v>
@@ -2557,33 +2572,33 @@
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>50</v>
+        <v>126</v>
       </c>
       <c r="K16" s="3">
-        <v>26</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>47</v>
+        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>178</v>
@@ -2592,33 +2607,33 @@
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="K17" s="3">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>178</v>
@@ -2627,33 +2642,33 @@
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>133</v>
+        <v>50</v>
       </c>
       <c r="K18" s="3">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>136</v>
+        <v>47</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>178</v>
@@ -2662,13 +2677,13 @@
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="K19" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -2679,16 +2694,16 @@
         <v>141</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="3">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3">
-        <v>24</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>178</v>
@@ -2697,33 +2712,33 @@
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="K20" s="3">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="3">
+        <v>27</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3">
-        <v>24</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>178</v>
@@ -2732,24 +2747,24 @@
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="K21" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>152</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>96</v>
+        <v>153</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
@@ -2758,7 +2773,7 @@
         <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>178</v>
@@ -2767,30 +2782,30 @@
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K22" s="3">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>157</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>53</v>
+        <v>107</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>158</v>
@@ -2808,27 +2823,27 @@
         <v>160</v>
       </c>
       <c r="K23" s="3">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>111</v>
+        <v>161</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>178</v>
@@ -2837,33 +2852,33 @@
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="K24" s="3">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E25" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>178</v>
@@ -2872,48 +2887,48 @@
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="K25" s="3">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>170</v>
+        <v>90</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>178</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>172</v>
+        <v>116</v>
       </c>
       <c r="K26" s="3">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
@@ -2924,13 +2939,13 @@
         <v>180</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>181</v>
@@ -2945,10 +2960,10 @@
         <v>182</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="K27" s="3">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28">
@@ -2956,54 +2971,54 @@
         <v>183</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>46</v>
+        <v>184</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>47</v>
+        <v>185</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E28" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>178</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>99</v>
+        <v>187</v>
       </c>
       <c r="K28" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E29" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>178</v>
@@ -3012,33 +3027,33 @@
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="K29" s="3">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>192</v>
+        <v>46</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>193</v>
+        <v>47</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
         <v>8</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>178</v>
@@ -3050,21 +3065,21 @@
         <v>194</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>195</v>
+        <v>110</v>
       </c>
       <c r="K30" s="3">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>197</v>
-      </c>
       <c r="C31" s="3" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
@@ -3073,7 +3088,7 @@
         <v>8</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>178</v>
@@ -3085,80 +3100,80 @@
         <v>198</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="K31" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>201</v>
+        <v>90</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="G32" s="3" t="s">
         <v>178</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="K32" s="3">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C33" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E33" s="3">
         <v>4</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>178</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I33" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="K33" s="3">
-        <v>5</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34">
@@ -3172,26 +3187,28 @@
         <v>212</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>0</v>
-      </c>
-      <c r="F34" s="3"/>
+        <v>4</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>213</v>
+      </c>
       <c r="G34" s="3" t="s">
         <v>178</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="K34" s="3">
-        <v>48</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -3215,7 +3232,7 @@
         <v>178</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>218</v>
@@ -3224,11 +3241,44 @@
         <v>219</v>
       </c>
       <c r="K35" s="3">
-        <v>41</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="K36" s="3">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K35"/>
+  <autoFilter ref="A1:K36"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3264,6 +3314,7 @@
     <hyperlink ref="I33" r:id="rId32"/>
     <hyperlink ref="I34" r:id="rId33"/>
     <hyperlink ref="I35" r:id="rId34"/>
+    <hyperlink ref="I36" r:id="rId35"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3271,11 +3322,11 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="29" customWidth="1"/>
+    <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
@@ -3305,48 +3356,48 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>191</v>
+        <v>57</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>192</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>188</v>
+        <v>60</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>194</v>
+        <v>61</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>195</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>196</v>
+        <v>88</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>197</v>
+        <v>89</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>188</v>
+        <v>91</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>198</v>
+        <v>92</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>195</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -3361,185 +3412,185 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B5" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="B6" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B9" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B10" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B11" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B12" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B14" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -3559,10 +3610,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2">
@@ -3570,10 +3621,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3">
@@ -3584,7 +3635,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="4">
@@ -3595,7 +3646,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
     </row>
     <row r="5">
@@ -3606,7 +3657,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6">
@@ -3617,7 +3668,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7">
@@ -3628,7 +3679,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
   </sheetData>
@@ -3649,13 +3700,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
     </row>
     <row r="2">
@@ -3666,7 +3717,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3678,7 +3729,7 @@
         <v>30</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3690,7 +3741,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W38.xlsx
+++ b/reports/devops-juniors-israel-2026-W38.xlsx
@@ -5,16 +5,15 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="🪜 Top Picks" sheetId="2" r:id="rId2"/>
     <sheet name="All Matches" sheetId="3" r:id="rId3"/>
-    <sheet name="🔥 New Today" sheetId="4" r:id="rId4"/>
-    <sheet name="Stack Demand" sheetId="5" r:id="rId5"/>
-    <sheet name="Buckets" sheetId="6" r:id="rId6"/>
-    <sheet name="Diagnostics" sheetId="7" r:id="rId7"/>
+    <sheet name="Stack Demand" sheetId="4" r:id="rId4"/>
+    <sheet name="Buckets" sheetId="5" r:id="rId5"/>
+    <sheet name="Diagnostics" sheetId="6" r:id="rId6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +30,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-16T11:24:46</t>
+    <t xml:space="preserve">2026-09-17T11:33:16</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -151,6 +150,24 @@
     <t xml:space="preserve">First Seen</t>
   </si>
   <si>
+    <t xml:space="preserve">Associate Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/associate-development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
     <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
   </si>
   <si>
@@ -187,24 +204,6 @@
     <t xml:space="preserve">2026-09-09</t>
   </si>
   <si>
-    <t xml:space="preserve">Associate Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/associate-development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOC Team Leader</t>
   </si>
   <si>
@@ -382,39 +381,27 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator 7992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator 7992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gini-Apps</t>
   </si>
   <si>
@@ -424,18 +411,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
   </si>
   <si>
-    <t xml:space="preserve">Communication System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ceva, Inc.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/communication-system-engineer-at-ceva-inc-4459357209</t>
-  </si>
-  <si>
     <t xml:space="preserve">Support Engineer</t>
   </si>
   <si>
@@ -508,7 +483,10 @@
     <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4444274357</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
@@ -535,6 +513,33 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4459788315</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia/Scotland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
@@ -553,33 +558,6 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia/Scotland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior System Administrator</t>
   </si>
   <si>
@@ -601,66 +579,57 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PassportCard</t>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
   </si>
   <si>
     <t xml:space="preserve">Monitoring, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-passportcard-4458103759</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Engineer II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWeber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uluberia-II,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-10</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4467707893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations Engineer II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWeber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uluberia-II,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
-  </si>
-  <si>
     <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
   </si>
   <si>
@@ -700,33 +669,33 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
@@ -769,16 +738,16 @@
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active Directory</t>
   </si>
   <si>
     <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -939,7 +908,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -947,7 +916,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -955,7 +924,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -963,7 +932,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>479</v>
+        <v>470</v>
       </c>
     </row>
     <row r="10">
@@ -1045,7 +1014,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1103,7 +1072,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
@@ -1187,7 +1156,7 @@
         <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1219,7 +1188,7 @@
         <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1251,7 +1220,7 @@
         <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -1280,7 +1249,7 @@
         <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>25</v>
@@ -1298,7 +1267,7 @@
         <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
@@ -1312,7 +1281,7 @@
         <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
@@ -1362,7 +1331,7 @@
         <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="8">
@@ -1408,7 +1377,7 @@
         <v>84</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>27</v>
@@ -1458,7 +1427,7 @@
         <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -1618,7 +1587,7 @@
         <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
@@ -1632,25 +1601,25 @@
         <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
@@ -1658,19 +1627,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>130</v>
@@ -1682,7 +1651,7 @@
         <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -1690,19 +1659,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F18" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>134</v>
@@ -1714,7 +1683,7 @@
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>50</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19">
@@ -1722,31 +1691,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F19" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20">
@@ -1754,31 +1723,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21">
@@ -1786,31 +1755,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="22">
@@ -1818,13 +1787,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -1833,16 +1802,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23">
@@ -1850,31 +1819,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24">
@@ -1882,10 +1851,10 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>90</v>
@@ -1894,19 +1863,19 @@
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25">
@@ -1914,31 +1883,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26">
@@ -1946,31 +1915,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F26" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2023,7 +1992,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2038,22 +2007,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2">
@@ -2067,7 +2036,7 @@
         <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2076,7 +2045,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2088,7 +2057,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -2102,7 +2071,7 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2111,7 +2080,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2123,7 +2092,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -2137,7 +2106,7 @@
         <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
@@ -2146,7 +2115,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2158,7 +2127,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -2169,7 +2138,7 @@
         <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>25</v>
@@ -2181,7 +2150,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2190,10 +2159,10 @@
         <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K5" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -2204,7 +2173,7 @@
         <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
@@ -2216,7 +2185,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2228,7 +2197,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -2251,7 +2220,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2260,10 +2229,10 @@
         <v>76</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K7" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -2286,7 +2255,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
@@ -2298,7 +2267,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -2309,7 +2278,7 @@
         <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>27</v>
@@ -2321,7 +2290,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2333,7 +2302,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -2356,7 +2325,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2365,10 +2334,10 @@
         <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="K10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -2391,7 +2360,7 @@
         <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2403,7 +2372,7 @@
         <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
@@ -2426,7 +2395,7 @@
         <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2438,7 +2407,7 @@
         <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -2461,7 +2430,7 @@
         <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2473,7 +2442,7 @@
         <v>110</v>
       </c>
       <c r="K13" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -2496,7 +2465,7 @@
         <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2508,7 +2477,7 @@
         <v>116</v>
       </c>
       <c r="K14" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -2531,7 +2500,7 @@
         <v>120</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2540,10 +2509,10 @@
         <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K15" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2554,54 +2523,54 @@
         <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K16" s="3">
-        <v>65</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -2610,33 +2579,33 @@
         <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="K17" s="3">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E18" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
@@ -2645,126 +2614,126 @@
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>50</v>
+        <v>136</v>
       </c>
       <c r="K18" s="3">
-        <v>27</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E19" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="K19" s="3">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K20" s="3">
-        <v>33</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="K21" s="3">
-        <v>20</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
@@ -2773,65 +2742,65 @@
         <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K22" s="3">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>122</v>
+        <v>158</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K23" s="3">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>161</v>
+        <v>128</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>90</v>
@@ -2840,165 +2809,165 @@
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="K24" s="3">
-        <v>33</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="K25" s="3">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E26" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="K26" s="3">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="3">
+        <v>9</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E27" s="3">
-        <v>12</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>144</v>
+        <v>110</v>
       </c>
       <c r="K27" s="3">
-        <v>33</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>184</v>
+        <v>52</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>185</v>
+        <v>53</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>187</v>
+        <v>110</v>
       </c>
       <c r="K28" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
@@ -3009,19 +2978,19 @@
         <v>189</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>190</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
@@ -3030,255 +2999,150 @@
         <v>191</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>110</v>
+        <v>192</v>
       </c>
       <c r="K29" s="3">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>46</v>
+        <v>194</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>47</v>
+        <v>195</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>110</v>
+        <v>198</v>
       </c>
       <c r="K30" s="3">
-        <v>21</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>113</v>
+        <v>201</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="K31" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>90</v>
+        <v>207</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3">
-        <v>8</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>197</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="K32" s="3">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>4</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>207</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="K33" s="3">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E34" s="3">
-        <v>4</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K34" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="K35" s="3">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="3">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="K36" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K36"/>
+  <autoFilter ref="A1:K33"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3312,104 +3176,11 @@
     <hyperlink ref="I31" r:id="rId30"/>
     <hyperlink ref="I32" r:id="rId31"/>
     <hyperlink ref="I33" r:id="rId32"/>
-    <hyperlink ref="I34" r:id="rId33"/>
-    <hyperlink ref="I35" r:id="rId34"/>
-    <hyperlink ref="I36" r:id="rId35"/>
   </hyperlinks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <cols>
-    <col min="1" max="1" width="43" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="60" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" s="3">
-        <v>100</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" s="3">
-        <v>60</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:G3"/>
-  <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F3" r:id="rId2"/>
-  </hyperlinks>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3419,185 +3190,185 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="B4" s="3">
         <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -3610,10 +3381,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2">
@@ -3621,10 +3392,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
     </row>
     <row r="3">
@@ -3635,7 +3406,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
     </row>
     <row r="4">
@@ -3646,7 +3417,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5">
@@ -3657,7 +3428,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">
@@ -3668,7 +3439,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7">
@@ -3679,14 +3450,14 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -3700,13 +3471,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2">
@@ -3714,10 +3485,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3726,10 +3497,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3741,7 +3512,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W38.xlsx
+++ b/reports/devops-juniors-israel-2026-W38.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="261">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17T11:33:16</t>
+    <t xml:space="preserve">2026-09-18T11:06:05</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -381,6 +381,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Administrator 7992</t>
   </si>
   <si>
@@ -399,9 +414,6 @@
     <t xml:space="preserve">2026-09-14</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gini-Apps</t>
   </si>
   <si>
@@ -525,13 +537,31 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
     <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Optimove</t>
   </si>
   <si>
-    <t xml:space="preserve">Estonia/Scotland</t>
+    <t xml:space="preserve">Estonia</t>
   </si>
   <si>
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
@@ -540,24 +570,6 @@
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior System Administrator</t>
   </si>
   <si>
@@ -687,13 +699,13 @@
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
     <t xml:space="preserve">Python</t>
@@ -908,7 +920,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -924,7 +936,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -1014,7 +1026,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -1072,7 +1084,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
@@ -1601,25 +1613,25 @@
         <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="17">
@@ -1627,19 +1639,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>130</v>
@@ -1651,7 +1663,7 @@
         <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>56</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -1659,19 +1671,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>134</v>
@@ -1683,7 +1695,7 @@
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -1691,13 +1703,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="D19" s="3" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>27</v>
@@ -1706,16 +1718,16 @@
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>140</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="20">
@@ -1723,31 +1735,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="E20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3">
+        <v>27</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F20" s="3">
-        <v>24</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="21">
@@ -1755,13 +1767,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>25</v>
@@ -1787,13 +1799,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="D22" s="3" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
@@ -1802,16 +1814,16 @@
         <v>24</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="23">
@@ -1819,31 +1831,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="D23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F23" s="3">
+        <v>24</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F23" s="3">
-        <v>23</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="24">
@@ -1851,19 +1863,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>163</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>164</v>
@@ -1875,7 +1887,7 @@
         <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25">
@@ -1883,13 +1895,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>167</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
@@ -1907,7 +1919,7 @@
         <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26">
@@ -1921,25 +1933,25 @@
         <v>171</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="3">
+        <v>12</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F26" s="3">
-        <v>10</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1992,7 +2004,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2007,22 +2019,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="2">
@@ -2045,7 +2057,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2057,7 +2069,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -2080,7 +2092,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2092,7 +2104,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
@@ -2115,7 +2127,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2127,7 +2139,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -2150,7 +2162,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2162,7 +2174,7 @@
         <v>56</v>
       </c>
       <c r="K5" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
@@ -2185,7 +2197,7 @@
         <v>69</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2197,7 +2209,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
@@ -2220,7 +2232,7 @@
         <v>75</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2232,7 +2244,7 @@
         <v>56</v>
       </c>
       <c r="K7" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -2255,7 +2267,7 @@
         <v>80</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>33</v>
@@ -2267,7 +2279,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -2290,7 +2302,7 @@
         <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2302,7 +2314,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -2325,7 +2337,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2337,7 +2349,7 @@
         <v>50</v>
       </c>
       <c r="K10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -2360,7 +2372,7 @@
         <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2372,7 +2384,7 @@
         <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12">
@@ -2395,7 +2407,7 @@
         <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2407,7 +2419,7 @@
         <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -2430,7 +2442,7 @@
         <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2442,7 +2454,7 @@
         <v>110</v>
       </c>
       <c r="K13" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
@@ -2465,7 +2477,7 @@
         <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2477,7 +2489,7 @@
         <v>116</v>
       </c>
       <c r="K14" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -2500,7 +2512,7 @@
         <v>120</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2512,7 +2524,7 @@
         <v>56</v>
       </c>
       <c r="K15" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2523,54 +2535,54 @@
         <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>124</v>
+        <v>59</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="K16" s="3">
-        <v>3</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>129</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
@@ -2579,33 +2591,33 @@
         <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>56</v>
+        <v>132</v>
       </c>
       <c r="K17" s="3">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
@@ -2614,21 +2626,21 @@
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>136</v>
+        <v>56</v>
       </c>
       <c r="K18" s="3">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="C19" s="3" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>27</v>
@@ -2637,68 +2649,68 @@
         <v>27</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G19" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="K19" s="3">
-        <v>21</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="D20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" s="3">
+        <v>27</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="3">
-        <v>24</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>148</v>
-      </c>
       <c r="K20" s="3">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>128</v>
+        <v>147</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>25</v>
@@ -2710,7 +2722,7 @@
         <v>150</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
@@ -2722,18 +2734,18 @@
         <v>152</v>
       </c>
       <c r="K21" s="3">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="C22" s="3" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
@@ -2742,80 +2754,80 @@
         <v>24</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="K22" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="3">
+        <v>24</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" s="3">
-        <v>23</v>
-      </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>162</v>
-      </c>
       <c r="K23" s="3">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>163</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>164</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
@@ -2824,21 +2836,21 @@
         <v>165</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>116</v>
+        <v>166</v>
       </c>
       <c r="K24" s="3">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>166</v>
+        <v>122</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>167</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
@@ -2850,7 +2862,7 @@
         <v>168</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
@@ -2859,10 +2871,10 @@
         <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="K25" s="3">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
@@ -2873,66 +2885,66 @@
         <v>171</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="3">
+        <v>12</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="3">
-        <v>10</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="G26" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
         <v>173</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="K26" s="3">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C27" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="D27" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E27" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="K27" s="3">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -2940,48 +2952,48 @@
         <v>185</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>52</v>
+        <v>186</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>53</v>
+        <v>149</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E28" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>110</v>
       </c>
       <c r="K28" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>189</v>
+        <v>52</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3">
         <v>8</v>
@@ -2990,7 +3002,7 @@
         <v>190</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
@@ -2999,124 +3011,126 @@
         <v>191</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>192</v>
+        <v>110</v>
       </c>
       <c r="K29" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E30" s="3">
+        <v>8</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="G30" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="3">
-        <v>4</v>
-      </c>
-      <c r="F30" s="3" t="s">
+      <c r="J30" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="K30" s="3">
-        <v>77</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>201</v>
-      </c>
       <c r="D31" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E31" s="3">
         <v>4</v>
       </c>
       <c r="F31" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>204</v>
-      </c>
       <c r="K31" s="3">
-        <v>7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="D32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3">
+        <v>4</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="K32" s="3">
-        <v>50</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
@@ -3126,23 +3140,56 @@
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H33" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="K33" s="3">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="K33" s="3">
-        <v>43</v>
+      <c r="I34" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="K34" s="3">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K33"/>
+  <autoFilter ref="A1:K34"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3176,6 +3223,7 @@
     <hyperlink ref="I31" r:id="rId30"/>
     <hyperlink ref="I32" r:id="rId31"/>
     <hyperlink ref="I33" r:id="rId32"/>
+    <hyperlink ref="I34" r:id="rId33"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3190,178 +3238,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B3" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B4" s="3">
         <v>17</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>202</v>
+        <v>228</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B8" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
   </sheetData>
@@ -3381,10 +3429,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2">
@@ -3392,10 +3440,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3">
@@ -3406,7 +3454,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4">
@@ -3417,7 +3465,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5">
@@ -3428,7 +3476,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6">
@@ -3439,7 +3487,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="7">
@@ -3450,7 +3498,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -3471,13 +3519,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2">
@@ -3485,10 +3533,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3497,10 +3545,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -3512,7 +3560,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W38.xlsx
+++ b/reports/devops-juniors-israel-2026-W38.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18T11:06:05</t>
+    <t xml:space="preserve">2026-09-20T11:13:22</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -944,7 +944,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>470</v>
+        <v>464</v>
       </c>
     </row>
     <row r="10">
@@ -2069,7 +2069,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -2104,7 +2104,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
@@ -2139,7 +2139,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -2174,7 +2174,7 @@
         <v>56</v>
       </c>
       <c r="K5" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6">
@@ -2209,7 +2209,7 @@
         <v>71</v>
       </c>
       <c r="K6" s="3">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -2244,7 +2244,7 @@
         <v>56</v>
       </c>
       <c r="K7" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -2279,7 +2279,7 @@
         <v>82</v>
       </c>
       <c r="K8" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9">
@@ -2314,7 +2314,7 @@
         <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -2349,7 +2349,7 @@
         <v>50</v>
       </c>
       <c r="K10" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -2384,7 +2384,7 @@
         <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -2419,7 +2419,7 @@
         <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -2454,7 +2454,7 @@
         <v>110</v>
       </c>
       <c r="K13" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14">
@@ -2489,7 +2489,7 @@
         <v>116</v>
       </c>
       <c r="K14" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -2524,7 +2524,7 @@
         <v>56</v>
       </c>
       <c r="K15" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -2559,7 +2559,7 @@
         <v>126</v>
       </c>
       <c r="K16" s="3">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17">
@@ -2594,7 +2594,7 @@
         <v>132</v>
       </c>
       <c r="K17" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -2629,7 +2629,7 @@
         <v>56</v>
       </c>
       <c r="K18" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -2664,7 +2664,7 @@
         <v>140</v>
       </c>
       <c r="K19" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -2699,7 +2699,7 @@
         <v>146</v>
       </c>
       <c r="K20" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -2734,7 +2734,7 @@
         <v>152</v>
       </c>
       <c r="K21" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -2769,7 +2769,7 @@
         <v>156</v>
       </c>
       <c r="K22" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -2804,7 +2804,7 @@
         <v>161</v>
       </c>
       <c r="K23" s="3">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
@@ -2839,7 +2839,7 @@
         <v>166</v>
       </c>
       <c r="K24" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -2874,7 +2874,7 @@
         <v>116</v>
       </c>
       <c r="K25" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26">
@@ -2909,7 +2909,7 @@
         <v>140</v>
       </c>
       <c r="K26" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
@@ -2944,7 +2944,7 @@
         <v>184</v>
       </c>
       <c r="K27" s="3">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
@@ -2979,7 +2979,7 @@
         <v>110</v>
       </c>
       <c r="K28" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
@@ -3014,7 +3014,7 @@
         <v>110</v>
       </c>
       <c r="K29" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30">
@@ -3049,7 +3049,7 @@
         <v>196</v>
       </c>
       <c r="K30" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -3084,7 +3084,7 @@
         <v>202</v>
       </c>
       <c r="K31" s="3">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32">
@@ -3119,7 +3119,7 @@
         <v>208</v>
       </c>
       <c r="K32" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33">
@@ -3152,7 +3152,7 @@
         <v>213</v>
       </c>
       <c r="K33" s="3">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="34">
@@ -3185,7 +3185,7 @@
         <v>218</v>
       </c>
       <c r="K34" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
